--- a/public/plantillas/tecnologia.xlsx
+++ b/public/plantillas/tecnologia.xlsx
@@ -1,47 +1,119 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Artículos" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Artículos" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Referencia Interna (código)</t>
+  </si>
+  <si>
+    <t>Coste</t>
+  </si>
+  <si>
+    <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Código de barras</t>
+  </si>
+  <si>
+    <t>Peso (gramos)</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Categoría</t>
+  </si>
+  <si>
+    <t>Nivel de ganancia</t>
+  </si>
+  <si>
+    <t>Origen</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Marca</t>
+  </si>
+  <si>
+    <t>Colección</t>
+  </si>
+  <si>
+    <t>Etiquetas</t>
+  </si>
+  <si>
+    <t>Proveedor</t>
+  </si>
+  <si>
+    <t>Punto de reorden</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Atributos JSON</t>
+  </si>
+  <si>
+    <t>Por cantidad</t>
+  </si>
+  <si>
+    <t>TEC-0001</t>
+  </si>
+  <si>
+    <t>7501234567892</t>
+  </si>
+  <si>
+    <t>Audífonos inalámbricos</t>
+  </si>
+  <si>
+    <t>Tecnología</t>
+  </si>
+  <si>
+    <t>Socio Comercial</t>
+  </si>
+  <si>
+    <t>importado</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>novedad</t>
+  </si>
+  <si>
+    <t>Audífonos bluetooth con estuche de carga</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -64,14 +136,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,87 +477,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R500"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="29.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="18.83203125" customWidth="1"/>
-    <col min="16" max="16" width="13.83203125" customWidth="1"/>
-    <col min="17" max="17" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tipo</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Referencia Interna (código)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Coste</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Cantidad</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Código de barras</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Peso (gramos)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Nombre</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Categoría</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Origen</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Material</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Marca</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Colección</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Etiquetas</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Proveedor</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Punto de reorden</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Descripción</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Atributos JSON</v>
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Por cantidad</v>
-      </c>
-      <c r="B2" t="str">
-        <v>TEC-0001</v>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
       </c>
       <c r="C2">
         <v>250</v>
@@ -484,49 +563,557 @@
       <c r="D2">
         <v>8</v>
       </c>
-      <c r="E2" t="str">
-        <v>7501234567892</v>
+      <c r="E2" t="s">
+        <v>20</v>
       </c>
       <c r="F2">
         <v>0.35</v>
       </c>
-      <c r="G2" t="str">
-        <v>Audífonos inalámbricos</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Tecnología</v>
-      </c>
-      <c r="I2" t="str">
-        <v>importado</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v>novedad</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2">
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2">
         <v>3</v>
       </c>
-      <c r="P2" t="str">
-        <v>Audífonos bluetooth con estuche de carga</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>{}</v>
+      <c r="Q2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
       </c>
     </row>
+    <row r="3" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="347" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="348" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="349" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="360" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="361" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="373" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="374" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="375" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="376" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="377" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="379" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="380" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="386" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="387" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="388" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="389" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="390" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="391" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="392" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="393" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="394" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="395" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="396" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="397" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="399" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="401" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="402" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="403" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="404" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="405" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="406" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="407" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="408" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="409" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="410" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="411" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="412" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="413" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="414" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="415" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="416" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="417" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="418" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="419" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="420" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="421" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="422" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="424" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="425" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="426" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="427" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="428" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="429" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="430" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="431" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="432" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="433" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="434" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="435" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="436" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="437" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="438" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="439" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="440" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="441" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="442" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="443" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="444" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="445" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="446" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="447" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="448" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="449" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="450" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="451" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="452" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="453" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="454" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="455" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="456" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="457" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="458" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="459" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="460" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="461" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="462" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="463" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="464" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="465" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="466" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="467" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="468" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="469" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="470" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="471" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="472" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="473" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="474" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="475" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="476" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="477" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="478" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="479" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="480" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="497" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="498" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="499" spans="9:9" x14ac:dyDescent="0.25"/>
+    <row r="500" spans="9:9" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q2"/>
-  </ignoredErrors>
+  <dataValidations count="2">
+    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Valor no válido" error="Elige uno de: Introducción, Socio Comercial, Importación" sqref="I10:I500">
+      <formula1>"Introducción,Socio Comercial,Importación"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorStyle="stop" errorTitle="Valor no válido" error="Elige uno de: Introducción, Socio Comercial, Importación" sqref="I2:I500">
+      <formula1>"Introducción,Socio Comercial,Importación"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>